--- a/data/raw/sales/Week 27/Audio_Array/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 27/Audio_Array/Vendor Sales (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,19 +531,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="I2" t="n">
-        <v>336237.37</v>
+        <v>464238.16</v>
       </c>
       <c r="J2" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -663,19 +663,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>19342.39</v>
+        <v>44032.23</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -861,13 +861,13 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>26690.7</v>
+        <v>41942.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -993,10 +993,10 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>16944.9</v>
+        <v>23333.04</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1191,13 +1191,13 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1736.44</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1323,13 +1323,13 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>2559.32</v>
+        <v>3320.34</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>17265.29</v>
+        <v>33329.71</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1455,10 +1455,10 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>23722.86</v>
+        <v>33177.94</v>
       </c>
       <c r="J16" t="n">
         <v>8</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         <v>18805.92</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I18" t="n">
-        <v>15887.28</v>
+        <v>17257.62</v>
       </c>
       <c r="J18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1653,10 +1653,10 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1355.08</v>
+        <v>2574.57</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1719,19 +1719,19 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>35103.14</v>
+        <v>41666.7</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1785,19 +1785,19 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="I21" t="n">
-        <v>382930.8</v>
+        <v>497659.51</v>
       </c>
       <c r="J21" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1851,10 +1851,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>3388.98</v>
+        <v>6608.47</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1917,10 +1917,10 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1983,13 +1983,13 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>3302.54</v>
+        <v>7438.13</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2049,13 +2049,13 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>6245.76</v>
+        <v>9185.59</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>6834.73</v>
+        <v>8105.07</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2181,19 +2181,19 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>55688.92</v>
+        <v>80760.12</v>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2313,13 +2313,13 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>15673.72</v>
+        <v>24569.5</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2379,13 +2379,13 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I30" t="n">
-        <v>77417.06</v>
+        <v>121895.89</v>
       </c>
       <c r="J30" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2445,13 +2445,13 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>5420.32</v>
+        <v>6733.04</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>677.12</v>
+        <v>1311.87</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2577,13 +2577,13 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>25417.83</v>
+        <v>33448.35</v>
       </c>
       <c r="J33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2775,13 +2775,13 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
-        <v>19614.05</v>
+        <v>23572.53</v>
       </c>
       <c r="J36" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2841,13 +2841,13 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>5114.31</v>
+        <v>7145.67</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2907,19 +2907,19 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
+        <v>43</v>
+      </c>
+      <c r="I38" t="n">
+        <v>189914.77</v>
+      </c>
+      <c r="J38" t="n">
         <v>38</v>
       </c>
-      <c r="I38" t="n">
-        <v>168944.42</v>
-      </c>
-      <c r="J38" t="n">
-        <v>36</v>
-      </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -2973,19 +2973,19 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I39" t="n">
-        <v>39411.06</v>
+        <v>51271.22</v>
       </c>
       <c r="J39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3039,19 +3039,19 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>20363.5</v>
+        <v>24149.08</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3171,19 +3171,19 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>9084.73</v>
+        <v>10998.29</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3369,13 +3369,13 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>1439.83</v>
+        <v>2837.29</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3501,13 +3501,13 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>40327.07</v>
+        <v>51849.09</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3567,13 +3567,13 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>8472.879999999999</v>
+        <v>15250.84</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3633,13 +3633,13 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>8091.52</v>
+        <v>14632.19</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3699,10 +3699,10 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3765,19 +3765,19 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I51" t="n">
-        <v>16819.48</v>
+        <v>22919.48</v>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3831,14 +3831,14 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>6677.96</v>
+      </c>
+      <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="I52" t="n">
-        <v>3458.47</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4227,19 +4227,19 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="I58" t="n">
-        <v>19909.34</v>
+        <v>29883.9</v>
       </c>
       <c r="J58" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4293,19 +4293,19 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I59" t="n">
-        <v>336370.5</v>
+        <v>481439.13</v>
       </c>
       <c r="J59" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4359,10 +4359,10 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>2117.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4425,19 +4425,19 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I61" t="n">
-        <v>22254.21</v>
+        <v>28350.81</v>
       </c>
       <c r="J61" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4491,19 +4491,19 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="I62" t="n">
-        <v>102361.75</v>
+        <v>152991.34</v>
       </c>
       <c r="J62" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4557,10 +4557,10 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>3261.86</v>
+        <v>6396.61</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4623,13 +4623,13 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>32201.69</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -4784,19 +4784,19 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>GB-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4824,16 +4824,16 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>2668.64</v>
+        <v>4405.93</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -4850,19 +4850,19 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4882,15 +4882,15 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>9999.870000000001</v>
+        <v>5210.17</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -4916,19 +4916,19 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4938,17 +4938,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>2795.76</v>
+        <v>9999.870000000001</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
@@ -4982,19 +4982,19 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5004,34 +5004,34 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>10166.97</v>
+        <v>5320.34</v>
       </c>
       <c r="J70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -5048,19 +5048,19 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5085,20 +5085,20 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" t="n">
+        <v>13585.6</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
         <v>2</v>
       </c>
-      <c r="I71" t="n">
-        <v>3461.02</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -5114,19 +5114,19 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5136,34 +5136,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>22931.17</v>
+        <v>3461.02</v>
       </c>
       <c r="J72" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -5180,19 +5180,19 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5217,19 +5217,19 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I73" t="n">
-        <v>58570.03</v>
+        <v>31617.57</v>
       </c>
       <c r="J73" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5246,19 +5246,19 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5268,34 +5268,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="I74" t="n">
-        <v>823.52</v>
+        <v>77328.46000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5312,19 +5312,19 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I75" t="n">
-        <v>33894.91</v>
+        <v>2277.76</v>
       </c>
       <c r="J75" t="n">
         <v>4</v>
@@ -5378,19 +5378,19 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5410,25 +5410,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>33894.91</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
         <v>2</v>
       </c>
-      <c r="I76" t="n">
-        <v>9559.33</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>1</v>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -5444,19 +5444,19 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5466,34 +5466,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>22616.91</v>
+        <v>9559.33</v>
       </c>
       <c r="J77" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -5510,19 +5510,19 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5542,24 +5542,24 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I78" t="n">
-        <v>11265.24</v>
+        <v>26342.35</v>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5576,19 +5576,19 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5598,34 +5598,34 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I79" t="n">
-        <v>2456.78</v>
+        <v>11265.24</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -5642,19 +5642,19 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1622.04</v>
+        <v>9574.58</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -5708,19 +5708,19 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5730,34 +5730,34 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>11394.91</v>
+        <v>2456.78</v>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5774,19 +5774,19 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5796,34 +5796,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>101764.41</v>
+        <v>1622.04</v>
       </c>
       <c r="J82" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5840,19 +5840,19 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5862,34 +5862,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>16477.96</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -5906,19 +5906,19 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5938,24 +5938,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>131105.14</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5972,19 +5972,19 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6004,24 +6004,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>63972.91</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -6038,19 +6038,19 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6070,24 +6070,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>14405.08</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -6104,19 +6104,19 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6126,35 +6126,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I87" t="n">
-        <v>2795.76</v>
+        <v>94476.31</v>
       </c>
       <c r="J87" t="n">
+        <v>14</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>2</v>
       </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -6170,19 +6170,19 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -6210,16 +6210,16 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>7626.27</v>
+        <v>6948.3</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6236,19 +6236,19 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6258,25 +6258,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
-        <v>8559.32</v>
+        <v>21183.89</v>
       </c>
       <c r="J89" t="n">
         <v>2</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -6302,19 +6302,19 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6324,35 +6324,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5549.14</v>
+      </c>
+      <c r="J90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>1</v>
       </c>
-      <c r="I90" t="n">
-        <v>3172.88</v>
-      </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -6368,19 +6368,19 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6390,34 +6390,34 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>4660.17</v>
+        <v>22535.59</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -6434,19 +6434,19 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -6474,16 +6474,16 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>6777.96</v>
+        <v>8559.32</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -6500,19 +6500,19 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6522,34 +6522,34 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I93" t="n">
-        <v>213903.48</v>
+        <v>12068.63</v>
       </c>
       <c r="J93" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -6566,19 +6566,19 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -6606,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1355.08</v>
+        <v>4660.17</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -6632,19 +6632,19 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6654,28 +6654,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I95" t="n">
-        <v>856.1900000000001</v>
+        <v>12708.46</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -6698,19 +6698,19 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6720,34 +6720,34 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="I96" t="n">
-        <v>761.86</v>
+        <v>285079.8</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -6764,19 +6764,19 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6801,13 +6801,13 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -6830,19 +6830,19 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6852,28 +6852,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>6574.58</v>
+        <v>856.1900000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -6896,19 +6896,19 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6918,51 +6918,249 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>761.86</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>27</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FBA80010</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AM-C52</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Microphone Dynamic</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vocal Microphone</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>27</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FBA80084</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BE-4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Audio Mixer</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>04 channels Mixer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
         <v>5</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I101" t="n">
+        <v>15724.58</v>
+      </c>
+      <c r="J101" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>27</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FBA80085</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Audio Mixer</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>06 channels Mixer</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>5</v>
+      </c>
+      <c r="I102" t="n">
         <v>29656.8</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J102" t="n">
         <v>6</v>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>1p Sales</t>
-        </is>
-      </c>
-      <c r="N99" t="n">
-        <v>27</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>27</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
